--- a/Design-Files/Transmitter433MHz-v1.0/Deliverables/BOM/eSpark-BOM-Transmitter_v1.0.xlsx
+++ b/Design-Files/Transmitter433MHz-v1.0/Deliverables/BOM/eSpark-BOM-Transmitter_v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\hasanmehmood-motordriver\Design-Files\Transmitter433MHz\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\hasanmehmood-motordriver\Design-Files\Transmitter433MHz-v1.0\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="176">
   <si>
     <t>Component list</t>
   </si>
@@ -529,6 +529,24 @@
   </si>
   <si>
     <t>Transmitter_v1.0.]</t>
+  </si>
+  <si>
+    <t>AC0402JRNPO9BN180</t>
+  </si>
+  <si>
+    <t>GRT155R61E105KE01D</t>
+  </si>
+  <si>
+    <t>GRT155R61E225KE13D</t>
+  </si>
+  <si>
+    <t>CL05C4R7CB51PNC</t>
+  </si>
+  <si>
+    <t>GRT1555C1H101JA02D</t>
+  </si>
+  <si>
+    <t>CL05C100JB51PNC</t>
   </si>
 </sst>
 </file>
@@ -1000,7 +1018,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1170,6 +1188,12 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1202,12 +1226,7 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1550,7 +1569,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:V34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="26" customWidth="1"/>
@@ -1571,9 +1590,10 @@
     <col min="17" max="17" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="20"/>
       <c r="C1" s="20"/>
@@ -1584,17 +1604,17 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="63"/>
-      <c r="M1" s="63"/>
-      <c r="N1" s="63"/>
-      <c r="O1" s="63"/>
-      <c r="P1" s="63"/>
-      <c r="Q1" s="63"/>
-      <c r="R1" s="63"/>
-      <c r="S1" s="64"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="65"/>
+      <c r="Q1" s="65"/>
+      <c r="R1" s="65"/>
+      <c r="S1" s="66"/>
     </row>
-    <row r="2" spans="1:19" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:22" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="21"/>
       <c r="C2" s="31"/>
@@ -1619,7 +1639,7 @@
       <c r="R2" s="4"/>
       <c r="S2" s="3"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22"/>
       <c r="C3" s="32"/>
@@ -1642,9 +1662,9 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="65"/>
+      <c r="S3" s="67"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="22"/>
       <c r="C4" s="32"/>
@@ -1667,9 +1687,9 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="66"/>
+      <c r="S4" s="68"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="22"/>
       <c r="C5" s="32"/>
@@ -1692,9 +1712,9 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="66"/>
+      <c r="S5" s="68"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="23"/>
       <c r="C6" s="33"/>
@@ -1713,9 +1733,9 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="66"/>
+      <c r="S6" s="68"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="24"/>
       <c r="C7" s="34"/>
@@ -1734,9 +1754,9 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="66"/>
+      <c r="S7" s="68"/>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="27"/>
       <c r="C8" s="35"/>
@@ -1755,9 +1775,9 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="66"/>
+      <c r="S8" s="68"/>
     </row>
-    <row r="9" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="30" t="s">
         <v>4</v>
@@ -1814,7 +1834,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="46">
         <f>ROW(B10) - ROW($B$9)</f>
@@ -1869,8 +1889,14 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="50"/>
+      <c r="U10" t="s">
+        <v>170</v>
+      </c>
+      <c r="V10" s="75" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="47">
         <f t="shared" ref="B11:B32" si="0">ROW(B11) - ROW($B$9)</f>
@@ -1925,8 +1951,14 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
+      <c r="U11" t="s">
+        <v>171</v>
+      </c>
+      <c r="V11" s="75" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="46">
         <f>ROW(B12) - ROW($B$9)</f>
@@ -1981,8 +2013,11 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="58"/>
+      <c r="V12" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="47">
         <f t="shared" si="0"/>
@@ -2037,8 +2072,14 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="58"/>
+      <c r="U13" t="s">
+        <v>172</v>
+      </c>
+      <c r="V13" s="75" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="46">
         <f>ROW(B14) - ROW($B$9)</f>
@@ -2093,8 +2134,14 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="58"/>
+      <c r="U14" t="s">
+        <v>173</v>
+      </c>
+      <c r="V14" s="75" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="47">
         <f t="shared" si="0"/>
@@ -2149,8 +2196,14 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="58"/>
+      <c r="U15" t="s">
+        <v>174</v>
+      </c>
+      <c r="V15" s="75" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="46">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -2205,8 +2258,14 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="58"/>
+      <c r="U16" t="s">
+        <v>175</v>
+      </c>
+      <c r="V16" s="75" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="17" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="47">
         <f t="shared" si="0"/>
@@ -2261,8 +2320,11 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="58"/>
+      <c r="V17" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="46">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -2317,8 +2379,11 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="58"/>
+      <c r="V18" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="19" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="47">
         <f t="shared" si="0"/>
@@ -2371,8 +2436,11 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="58"/>
+      <c r="V19" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="46">
         <f>ROW(B20) - ROW($B$9)</f>
@@ -2427,8 +2495,11 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="58"/>
+      <c r="V20" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="21" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="47">
         <f t="shared" si="0"/>
@@ -2483,8 +2554,11 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="58"/>
+      <c r="V21" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="22" spans="1:19" ht="24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="46">
         <f>ROW(B22) - ROW($B$9)</f>
@@ -2539,8 +2613,11 @@
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="58"/>
+      <c r="V22" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="23" spans="1:19" ht="36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" ht="36" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="47">
         <f t="shared" si="0"/>
@@ -2595,8 +2672,11 @@
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="58"/>
+      <c r="V23" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="46">
         <f>ROW(B24) - ROW($B$9)</f>
@@ -2651,8 +2731,11 @@
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="58"/>
+      <c r="V24" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="47">
         <f t="shared" si="0"/>
@@ -2707,8 +2790,11 @@
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="58"/>
+      <c r="V25" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="46">
         <f>ROW(B26) - ROW($B$9)</f>
@@ -2763,8 +2849,11 @@
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="58"/>
+      <c r="V26" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="47">
         <f t="shared" si="0"/>
@@ -2819,8 +2908,11 @@
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="58"/>
+      <c r="V27" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="46">
         <f>ROW(B28) - ROW($B$9)</f>
@@ -2875,8 +2967,11 @@
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="58"/>
+      <c r="V28" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="47">
         <f t="shared" si="0"/>
@@ -2931,8 +3026,11 @@
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="58"/>
+      <c r="V29" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="46">
         <f>ROW(B30) - ROW($B$9)</f>
@@ -2987,8 +3085,11 @@
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="58"/>
+      <c r="V30" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="31" spans="1:19" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="47">
         <f t="shared" si="0"/>
@@ -3043,9 +3144,12 @@
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="39"/>
+      <c r="V31" t="s">
+        <v>154</v>
+      </c>
     </row>
-    <row r="32" spans="1:19" s="74" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
+    <row r="32" spans="1:22" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="63"/>
       <c r="B32" s="47">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3099,6 +3203,9 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="39"/>
+      <c r="V32" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="33" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3114,17 +3221,17 @@
       <c r="K33" s="45"/>
       <c r="L33" s="45"/>
       <c r="M33" s="45"/>
-      <c r="N33" s="71" t="s">
+      <c r="N33" s="73" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="72"/>
-      <c r="P33" s="72"/>
+      <c r="O33" s="74"/>
+      <c r="P33" s="74"/>
       <c r="Q33" s="48">
         <f>SUM(Q10:Q32)</f>
         <v>18.846000000000004</v>
       </c>
-      <c r="R33" s="67"/>
-      <c r="S33" s="68"/>
+      <c r="R33" s="69"/>
+      <c r="S33" s="70"/>
     </row>
     <row r="34" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3140,17 +3247,17 @@
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
-      <c r="N34" s="71" t="s">
+      <c r="N34" s="73" t="s">
         <v>6</v>
       </c>
-      <c r="O34" s="72"/>
-      <c r="P34" s="72"/>
+      <c r="O34" s="74"/>
+      <c r="P34" s="74"/>
       <c r="Q34" s="49">
         <f>Q33/5</f>
         <v>3.7692000000000005</v>
       </c>
-      <c r="R34" s="69"/>
-      <c r="S34" s="70"/>
+      <c r="R34" s="71"/>
+      <c r="S34" s="72"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3184,9 +3291,15 @@
     <hyperlink ref="O12" r:id="rId21"/>
     <hyperlink ref="O25" r:id="rId22"/>
     <hyperlink ref="O32" r:id="rId23"/>
+    <hyperlink ref="V10" r:id="rId24"/>
+    <hyperlink ref="V11" r:id="rId25"/>
+    <hyperlink ref="V13" r:id="rId26"/>
+    <hyperlink ref="V14" r:id="rId27"/>
+    <hyperlink ref="V15" r:id="rId28"/>
+    <hyperlink ref="V16" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
-  <drawing r:id="rId25"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
+  <drawing r:id="rId31"/>
 </worksheet>
 </file>
--- a/Design-Files/Transmitter433MHz-v1.0/Deliverables/BOM/eSpark-BOM-Transmitter_v1.0.xlsx
+++ b/Design-Files/Transmitter433MHz-v1.0/Deliverables/BOM/eSpark-BOM-Transmitter_v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="182">
   <si>
     <t>Component list</t>
   </si>
@@ -186,9 +186,6 @@
     <t>RED LED 0603 Light Emitting Diodes</t>
   </si>
   <si>
-    <t>Zero Ohm Resistor, Jumper, 0402 [1005 Metric], Thick Film, 63 mW, 1 A, Surface Mount</t>
-  </si>
-  <si>
     <t>RES 100K OHM 1% 1/16W 0402</t>
   </si>
   <si>
@@ -547,6 +544,27 @@
   </si>
   <si>
     <t>CL05C100JB51PNC</t>
+  </si>
+  <si>
+    <t>ERJ-H2G0R00X</t>
+  </si>
+  <si>
+    <t>RESISTOR 0402 JUMPER ZERO OHM</t>
+  </si>
+  <si>
+    <t>CRCW0402100KFKED</t>
+  </si>
+  <si>
+    <t>CRCW0402300KFKED</t>
+  </si>
+  <si>
+    <t>Automotive already</t>
+  </si>
+  <si>
+    <t>CRCW040210K0FKEE</t>
+  </si>
+  <si>
+    <t>CRCW04023K30FKEDC</t>
   </si>
 </sst>
 </file>
@@ -1194,6 +1212,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1226,7 +1245,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1604,15 +1622,15 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="65"/>
-      <c r="L1" s="65"/>
-      <c r="M1" s="65"/>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-      <c r="P1" s="65"/>
-      <c r="Q1" s="65"/>
-      <c r="R1" s="65"/>
-      <c r="S1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="P1" s="66"/>
+      <c r="Q1" s="66"/>
+      <c r="R1" s="66"/>
+      <c r="S1" s="67"/>
     </row>
     <row r="2" spans="1:22" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -1623,7 +1641,7 @@
       </c>
       <c r="E2" s="11"/>
       <c r="F2" s="55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G2" s="12"/>
       <c r="H2" s="4"/>
@@ -1648,7 +1666,7 @@
       </c>
       <c r="E3" s="13"/>
       <c r="F3" s="56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G3" s="13"/>
       <c r="H3" s="5"/>
@@ -1662,7 +1680,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
-      <c r="S3" s="67"/>
+      <c r="S3" s="68"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
@@ -1673,7 +1691,7 @@
       </c>
       <c r="E4" s="13"/>
       <c r="F4" s="56" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G4" s="14"/>
       <c r="H4" s="7"/>
@@ -1687,7 +1705,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="6"/>
       <c r="R4" s="6"/>
-      <c r="S4" s="68"/>
+      <c r="S4" s="69"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
@@ -1712,7 +1730,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
-      <c r="S5" s="68"/>
+      <c r="S5" s="69"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
@@ -1733,7 +1751,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="6"/>
       <c r="R6" s="6"/>
-      <c r="S6" s="68"/>
+      <c r="S6" s="69"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
@@ -1754,7 +1772,7 @@
       <c r="P7" s="8"/>
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
-      <c r="S7" s="68"/>
+      <c r="S7" s="69"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1775,7 +1793,7 @@
       <c r="P8" s="8"/>
       <c r="Q8" s="8"/>
       <c r="R8" s="8"/>
-      <c r="S8" s="68"/>
+      <c r="S8" s="69"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
@@ -1792,46 +1810,46 @@
         <v>41</v>
       </c>
       <c r="F9" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G9" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H9" s="30" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I9" s="30" t="s">
+        <v>144</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="J9" s="30" t="s">
-        <v>108</v>
-      </c>
-      <c r="K9" s="30" t="s">
+      <c r="L9" s="30" t="s">
+        <v>143</v>
+      </c>
+      <c r="M9" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="L9" s="30" t="s">
-        <v>144</v>
-      </c>
-      <c r="M9" s="30" t="s">
+      <c r="N9" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="N9" s="30" t="s">
+      <c r="O9" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="O9" s="30" t="s">
+      <c r="P9" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="P9" s="30" t="s">
+      <c r="Q9" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="Q9" s="30" t="s">
+      <c r="R9" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="R9" s="30" t="s">
+      <c r="S9" s="30" t="s">
         <v>152</v>
-      </c>
-      <c r="S9" s="30" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
@@ -1850,22 +1868,22 @@
         <v>42</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G10" s="37" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I10" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L10" s="37">
         <v>2</v>
@@ -1878,7 +1896,7 @@
         <v>20</v>
       </c>
       <c r="O10" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P10" s="38">
         <v>2.3699999999999999E-2</v>
@@ -1890,10 +1908,10 @@
       <c r="R10" s="37"/>
       <c r="S10" s="50"/>
       <c r="U10" t="s">
-        <v>170</v>
-      </c>
-      <c r="V10" s="75" t="s">
-        <v>154</v>
+        <v>169</v>
+      </c>
+      <c r="V10" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
@@ -1912,22 +1930,22 @@
         <v>43</v>
       </c>
       <c r="F11" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I11" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J11" s="51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="K11" s="51" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L11" s="51">
         <v>1</v>
@@ -1940,7 +1958,7 @@
         <v>50</v>
       </c>
       <c r="O11" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P11" s="52">
         <v>7.3000000000000001E-3</v>
@@ -1952,10 +1970,10 @@
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
       <c r="U11" t="s">
-        <v>171</v>
-      </c>
-      <c r="V11" s="75" t="s">
-        <v>154</v>
+        <v>170</v>
+      </c>
+      <c r="V11" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
@@ -1974,22 +1992,22 @@
         <v>44</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G12" s="61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I12" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="J12" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="J12" s="37" t="s">
-        <v>159</v>
-      </c>
       <c r="K12" s="37" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L12" s="37">
         <v>1</v>
@@ -2002,7 +2020,7 @@
         <v>100</v>
       </c>
       <c r="O12" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P12" s="38">
         <v>2.2000000000000001E-3</v>
@@ -2014,7 +2032,7 @@
       <c r="R12" s="37"/>
       <c r="S12" s="58"/>
       <c r="V12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
@@ -2033,22 +2051,22 @@
         <v>45</v>
       </c>
       <c r="F13" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G13" s="51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I13" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K13" s="51" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="L13" s="51">
         <v>1</v>
@@ -2061,7 +2079,7 @@
         <v>20</v>
       </c>
       <c r="O13" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P13" s="52">
         <v>2.1399999999999999E-2</v>
@@ -2073,10 +2091,10 @@
       <c r="R13" s="51"/>
       <c r="S13" s="58"/>
       <c r="U13" t="s">
-        <v>172</v>
-      </c>
-      <c r="V13" s="75" t="s">
-        <v>154</v>
+        <v>171</v>
+      </c>
+      <c r="V13" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
@@ -2095,22 +2113,22 @@
         <v>46</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14" s="37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I14" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L14" s="37">
         <v>1</v>
@@ -2123,7 +2141,7 @@
         <v>100</v>
       </c>
       <c r="O14" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P14" s="38">
         <v>2.3999999999999998E-3</v>
@@ -2135,10 +2153,10 @@
       <c r="R14" s="37"/>
       <c r="S14" s="58"/>
       <c r="U14" t="s">
-        <v>173</v>
-      </c>
-      <c r="V14" s="75" t="s">
-        <v>154</v>
+        <v>172</v>
+      </c>
+      <c r="V14" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
@@ -2157,22 +2175,22 @@
         <v>47</v>
       </c>
       <c r="F15" s="51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15" s="51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H15" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I15" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J15" s="51" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K15" s="51" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L15" s="51">
         <v>1</v>
@@ -2185,7 +2203,7 @@
         <v>100</v>
       </c>
       <c r="O15" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P15" s="52">
         <v>1E-3</v>
@@ -2197,10 +2215,10 @@
       <c r="R15" s="51"/>
       <c r="S15" s="58"/>
       <c r="U15" t="s">
-        <v>174</v>
-      </c>
-      <c r="V15" s="75" t="s">
-        <v>154</v>
+        <v>173</v>
+      </c>
+      <c r="V15" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
@@ -2219,22 +2237,22 @@
         <v>48</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G16" s="37" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I16" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J16" s="37" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K16" s="37" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L16" s="37">
         <v>1</v>
@@ -2247,7 +2265,7 @@
         <v>100</v>
       </c>
       <c r="O16" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P16" s="38">
         <v>2.2000000000000001E-3</v>
@@ -2259,10 +2277,10 @@
       <c r="R16" s="37"/>
       <c r="S16" s="58"/>
       <c r="U16" t="s">
-        <v>175</v>
-      </c>
-      <c r="V16" s="75" t="s">
-        <v>154</v>
+        <v>174</v>
+      </c>
+      <c r="V16" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="24" x14ac:dyDescent="0.25">
@@ -2281,22 +2299,22 @@
         <v>49</v>
       </c>
       <c r="F17" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H17" s="51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I17" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J17" s="51" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="K17" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L17" s="51">
         <v>1</v>
@@ -2309,7 +2327,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P17" s="52">
         <v>9.5399999999999999E-2</v>
@@ -2321,7 +2339,7 @@
       <c r="R17" s="51"/>
       <c r="S17" s="58"/>
       <c r="V17" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
@@ -2340,22 +2358,22 @@
         <v>50</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G18" s="61">
         <v>8266292</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I18" s="37" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J18" s="37" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K18" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L18" s="37">
         <v>1</v>
@@ -2368,7 +2386,7 @@
         <v>20</v>
       </c>
       <c r="O18" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P18" s="38">
         <v>2.1999999999999999E-2</v>
@@ -2380,7 +2398,7 @@
       <c r="R18" s="37"/>
       <c r="S18" s="58"/>
       <c r="V18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="24" x14ac:dyDescent="0.25">
@@ -2399,19 +2417,19 @@
         <v>51</v>
       </c>
       <c r="F19" s="51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G19" s="51" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H19" s="51" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I19" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J19" s="51" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K19" s="51"/>
       <c r="L19" s="51">
@@ -2425,7 +2443,7 @@
         <v>50</v>
       </c>
       <c r="O19" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P19" s="52">
         <v>4.4999999999999997E-3</v>
@@ -2437,7 +2455,7 @@
       <c r="R19" s="51"/>
       <c r="S19" s="58"/>
       <c r="V19" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2456,22 +2474,22 @@
         <v>52</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I20" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J20" s="37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K20" s="37" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L20" s="37">
         <v>1</v>
@@ -2484,7 +2502,7 @@
         <v>50</v>
       </c>
       <c r="O20" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P20" s="38">
         <v>8.8999999999999999E-3</v>
@@ -2496,7 +2514,7 @@
       <c r="R20" s="37"/>
       <c r="S20" s="58"/>
       <c r="V20" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="24" x14ac:dyDescent="0.25">
@@ -2515,22 +2533,22 @@
         <v>53</v>
       </c>
       <c r="F21" s="51" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" s="51" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H21" s="51" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I21" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J21" s="51" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K21" s="51" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L21" s="51">
         <v>1</v>
@@ -2543,7 +2561,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P21" s="52">
         <v>5.5899999999999998E-2</v>
@@ -2555,7 +2573,7 @@
       <c r="R21" s="51"/>
       <c r="S21" s="58"/>
       <c r="V21" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="24" x14ac:dyDescent="0.25">
@@ -2574,22 +2592,22 @@
         <v>54</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G22" s="37" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I22" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J22" s="37" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K22" s="37" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L22" s="37">
         <v>1</v>
@@ -2602,7 +2620,7 @@
         <v>20</v>
       </c>
       <c r="O22" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P22" s="38">
         <v>2.0799999999999999E-2</v>
@@ -2614,10 +2632,10 @@
       <c r="R22" s="37"/>
       <c r="S22" s="58"/>
       <c r="V22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="36" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="47">
         <f t="shared" si="0"/>
@@ -2630,25 +2648,25 @@
         <v>32</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>55</v>
+        <v>176</v>
       </c>
       <c r="F23" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G23" s="51" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="H23" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I23" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="K23" s="51" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L23" s="51">
         <v>2</v>
@@ -2661,7 +2679,7 @@
         <v>100</v>
       </c>
       <c r="O23" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P23" s="52">
         <v>1E-3</v>
@@ -2672,8 +2690,11 @@
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="58"/>
-      <c r="V23" t="s">
-        <v>154</v>
+      <c r="U23" t="s">
+        <v>175</v>
+      </c>
+      <c r="V23" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
@@ -2689,25 +2710,25 @@
         <v>33</v>
       </c>
       <c r="E24" s="37" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G24" s="37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I24" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J24" s="37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K24" s="37" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L24" s="37">
         <v>1</v>
@@ -2720,7 +2741,7 @@
         <v>100</v>
       </c>
       <c r="O24" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P24" s="38">
         <v>5.9999999999999995E-4</v>
@@ -2731,8 +2752,11 @@
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="58"/>
-      <c r="V24" t="s">
-        <v>154</v>
+      <c r="U24" t="s">
+        <v>177</v>
+      </c>
+      <c r="V24" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
@@ -2748,25 +2772,25 @@
         <v>34</v>
       </c>
       <c r="E25" s="51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="F25" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G25" s="62" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H25" s="51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I25" s="51" t="s">
+        <v>159</v>
+      </c>
+      <c r="J25" s="51" t="s">
         <v>160</v>
       </c>
-      <c r="J25" s="51" t="s">
-        <v>161</v>
-      </c>
       <c r="K25" s="51" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L25" s="51">
         <v>1</v>
@@ -2779,7 +2803,7 @@
         <v>100</v>
       </c>
       <c r="O25" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P25" s="52">
         <v>1.1000000000000001E-3</v>
@@ -2790,8 +2814,11 @@
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="58"/>
-      <c r="V25" t="s">
-        <v>154</v>
+      <c r="U25" t="s">
+        <v>178</v>
+      </c>
+      <c r="V25" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
@@ -2807,25 +2834,25 @@
         <v>35</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I26" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J26" s="37" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K26" s="37" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="L26" s="37">
         <v>1</v>
@@ -2838,7 +2865,7 @@
         <v>20</v>
       </c>
       <c r="O26" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P26" s="38">
         <v>3.3300000000000003E-2</v>
@@ -2849,8 +2876,11 @@
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="58"/>
+      <c r="U26" t="s">
+        <v>179</v>
+      </c>
       <c r="V26" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
@@ -2866,25 +2896,25 @@
         <v>36</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G27" s="51" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H27" s="51" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I27" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J27" s="51" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K27" s="51" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="L27" s="51">
         <v>1</v>
@@ -2897,7 +2927,7 @@
         <v>20</v>
       </c>
       <c r="O27" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P27" s="52">
         <v>0.02</v>
@@ -2908,8 +2938,11 @@
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="58"/>
-      <c r="V27" t="s">
-        <v>154</v>
+      <c r="U27" t="s">
+        <v>180</v>
+      </c>
+      <c r="V27" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
@@ -2925,25 +2958,25 @@
         <v>37</v>
       </c>
       <c r="E28" s="37" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G28" s="37" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="I28" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J28" s="37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K28" s="37" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="L28" s="37">
         <v>1</v>
@@ -2956,7 +2989,7 @@
         <v>100</v>
       </c>
       <c r="O28" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P28" s="38">
         <v>6.9999999999999999E-4</v>
@@ -2967,8 +3000,11 @@
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="58"/>
-      <c r="V28" t="s">
-        <v>154</v>
+      <c r="U28" t="s">
+        <v>181</v>
+      </c>
+      <c r="V28" s="65" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
@@ -2984,25 +3020,25 @@
         <v>38</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F29" s="51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G29" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H29" s="51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I29" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J29" s="51" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K29" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L29" s="51">
         <v>1</v>
@@ -3015,7 +3051,7 @@
         <v>10</v>
       </c>
       <c r="O29" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P29" s="52">
         <v>9.98E-2</v>
@@ -3027,7 +3063,7 @@
       <c r="R29" s="51"/>
       <c r="S29" s="58"/>
       <c r="V29" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
@@ -3043,25 +3079,25 @@
         <v>39</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I30" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J30" s="37" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K30" s="37" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L30" s="37">
         <v>1</v>
@@ -3074,7 +3110,7 @@
         <v>10</v>
       </c>
       <c r="O30" s="59" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P30" s="38">
         <v>4.8000000000000001E-2</v>
@@ -3086,7 +3122,7 @@
       <c r="R30" s="37"/>
       <c r="S30" s="58"/>
       <c r="V30" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3102,25 +3138,25 @@
         <v>40</v>
       </c>
       <c r="E31" s="51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F31" s="51" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G31" s="51" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H31" s="51" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I31" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J31" s="51" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K31" s="51" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="L31" s="51">
         <v>1</v>
@@ -3133,7 +3169,7 @@
         <v>10</v>
       </c>
       <c r="O31" s="60" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P31" s="52">
         <v>5.2600000000000001E-2</v>
@@ -3145,7 +3181,7 @@
       <c r="R31" s="51"/>
       <c r="S31" s="39"/>
       <c r="V31" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:22" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -3155,31 +3191,31 @@
         <v>23</v>
       </c>
       <c r="C32" s="54" t="s">
+        <v>162</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="E32" s="51" t="s">
         <v>163</v>
       </c>
-      <c r="D32" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="51" t="s">
+      <c r="F32" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="G32" s="51" t="s">
         <v>164</v>
       </c>
-      <c r="F32" s="51" t="s">
-        <v>155</v>
-      </c>
-      <c r="G32" s="51" t="s">
+      <c r="H32" s="51" t="s">
         <v>165</v>
       </c>
-      <c r="H32" s="51" t="s">
-        <v>166</v>
-      </c>
       <c r="I32" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J32" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K32" s="51" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L32" s="51">
         <v>1</v>
@@ -3192,7 +3228,7 @@
         <v>5</v>
       </c>
       <c r="O32" s="60" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P32" s="52">
         <v>2.0699999999999998</v>
@@ -3204,7 +3240,7 @@
       <c r="R32" s="51"/>
       <c r="S32" s="39"/>
       <c r="V32" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -3221,17 +3257,17 @@
       <c r="K33" s="45"/>
       <c r="L33" s="45"/>
       <c r="M33" s="45"/>
-      <c r="N33" s="73" t="s">
+      <c r="N33" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="74"/>
-      <c r="P33" s="74"/>
+      <c r="O33" s="75"/>
+      <c r="P33" s="75"/>
       <c r="Q33" s="48">
         <f>SUM(Q10:Q32)</f>
         <v>18.846000000000004</v>
       </c>
-      <c r="R33" s="69"/>
-      <c r="S33" s="70"/>
+      <c r="R33" s="70"/>
+      <c r="S33" s="71"/>
     </row>
     <row r="34" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
@@ -3247,17 +3283,17 @@
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
       <c r="M34" s="10"/>
-      <c r="N34" s="73" t="s">
+      <c r="N34" s="74" t="s">
         <v>6</v>
       </c>
-      <c r="O34" s="74"/>
-      <c r="P34" s="74"/>
+      <c r="O34" s="75"/>
+      <c r="P34" s="75"/>
       <c r="Q34" s="49">
         <f>Q33/5</f>
         <v>3.7692000000000005</v>
       </c>
-      <c r="R34" s="71"/>
-      <c r="S34" s="72"/>
+      <c r="R34" s="72"/>
+      <c r="S34" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -3297,9 +3333,14 @@
     <hyperlink ref="V14" r:id="rId27"/>
     <hyperlink ref="V15" r:id="rId28"/>
     <hyperlink ref="V16" r:id="rId29"/>
+    <hyperlink ref="V24" r:id="rId30"/>
+    <hyperlink ref="V23" r:id="rId31"/>
+    <hyperlink ref="V25" r:id="rId32"/>
+    <hyperlink ref="V27" r:id="rId33"/>
+    <hyperlink ref="V28" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
-  <drawing r:id="rId31"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
+  <drawing r:id="rId36"/>
 </worksheet>
 </file>
--- a/Design-Files/Transmitter433MHz-v1.0/Deliverables/BOM/eSpark-BOM-Transmitter_v1.0.xlsx
+++ b/Design-Files/Transmitter433MHz-v1.0/Deliverables/BOM/eSpark-BOM-Transmitter_v1.0.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="170">
   <si>
     <t>Component list</t>
   </si>
@@ -528,43 +528,7 @@
     <t>Transmitter_v1.0.]</t>
   </si>
   <si>
-    <t>AC0402JRNPO9BN180</t>
-  </si>
-  <si>
-    <t>GRT155R61E105KE01D</t>
-  </si>
-  <si>
-    <t>GRT155R61E225KE13D</t>
-  </si>
-  <si>
-    <t>CL05C4R7CB51PNC</t>
-  </si>
-  <si>
-    <t>GRT1555C1H101JA02D</t>
-  </si>
-  <si>
-    <t>CL05C100JB51PNC</t>
-  </si>
-  <si>
-    <t>ERJ-H2G0R00X</t>
-  </si>
-  <si>
     <t>RESISTOR 0402 JUMPER ZERO OHM</t>
-  </si>
-  <si>
-    <t>CRCW0402100KFKED</t>
-  </si>
-  <si>
-    <t>CRCW0402300KFKED</t>
-  </si>
-  <si>
-    <t>Automotive already</t>
-  </si>
-  <si>
-    <t>CRCW040210K0FKEE</t>
-  </si>
-  <si>
-    <t>CRCW04023K30FKEDC</t>
   </si>
 </sst>
 </file>
@@ -1907,12 +1871,7 @@
       </c>
       <c r="R10" s="37"/>
       <c r="S10" s="50"/>
-      <c r="U10" t="s">
-        <v>169</v>
-      </c>
-      <c r="V10" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V10" s="65"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
@@ -1969,12 +1928,7 @@
       </c>
       <c r="R11" s="51"/>
       <c r="S11" s="51"/>
-      <c r="U11" t="s">
-        <v>170</v>
-      </c>
-      <c r="V11" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V11" s="65"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
@@ -2031,9 +1985,6 @@
       </c>
       <c r="R12" s="37"/>
       <c r="S12" s="58"/>
-      <c r="V12" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
@@ -2090,12 +2041,7 @@
       </c>
       <c r="R13" s="51"/>
       <c r="S13" s="58"/>
-      <c r="U13" t="s">
-        <v>171</v>
-      </c>
-      <c r="V13" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V13" s="65"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
@@ -2152,12 +2098,7 @@
       </c>
       <c r="R14" s="37"/>
       <c r="S14" s="58"/>
-      <c r="U14" t="s">
-        <v>172</v>
-      </c>
-      <c r="V14" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V14" s="65"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
@@ -2214,12 +2155,7 @@
       </c>
       <c r="R15" s="51"/>
       <c r="S15" s="58"/>
-      <c r="U15" t="s">
-        <v>173</v>
-      </c>
-      <c r="V15" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V15" s="65"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
@@ -2276,12 +2212,7 @@
       </c>
       <c r="R16" s="37"/>
       <c r="S16" s="58"/>
-      <c r="U16" t="s">
-        <v>174</v>
-      </c>
-      <c r="V16" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V16" s="65"/>
     </row>
     <row r="17" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
@@ -2338,9 +2269,6 @@
       </c>
       <c r="R17" s="51"/>
       <c r="S17" s="58"/>
-      <c r="V17" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
@@ -2397,9 +2325,6 @@
       </c>
       <c r="R18" s="37"/>
       <c r="S18" s="58"/>
-      <c r="V18" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="19" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
@@ -2454,9 +2379,6 @@
       </c>
       <c r="R19" s="51"/>
       <c r="S19" s="58"/>
-      <c r="V19" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
@@ -2513,9 +2435,6 @@
       </c>
       <c r="R20" s="37"/>
       <c r="S20" s="58"/>
-      <c r="V20" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="21" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
@@ -2572,9 +2491,6 @@
       </c>
       <c r="R21" s="51"/>
       <c r="S21" s="58"/>
-      <c r="V21" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="22" spans="1:22" ht="24" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
@@ -2631,9 +2547,6 @@
       </c>
       <c r="R22" s="37"/>
       <c r="S22" s="58"/>
-      <c r="V22" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
@@ -2648,7 +2561,7 @@
         <v>32</v>
       </c>
       <c r="E23" s="51" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F23" s="51" t="s">
         <v>71</v>
@@ -2690,12 +2603,7 @@
       </c>
       <c r="R23" s="51"/>
       <c r="S23" s="58"/>
-      <c r="U23" t="s">
-        <v>175</v>
-      </c>
-      <c r="V23" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V23" s="65"/>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
@@ -2752,12 +2660,7 @@
       </c>
       <c r="R24" s="37"/>
       <c r="S24" s="58"/>
-      <c r="U24" t="s">
-        <v>177</v>
-      </c>
-      <c r="V24" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V24" s="65"/>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
@@ -2814,12 +2717,7 @@
       </c>
       <c r="R25" s="51"/>
       <c r="S25" s="58"/>
-      <c r="U25" t="s">
-        <v>178</v>
-      </c>
-      <c r="V25" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V25" s="65"/>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
@@ -2876,12 +2774,6 @@
       </c>
       <c r="R26" s="37"/>
       <c r="S26" s="58"/>
-      <c r="U26" t="s">
-        <v>179</v>
-      </c>
-      <c r="V26" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
@@ -2938,12 +2830,7 @@
       </c>
       <c r="R27" s="51"/>
       <c r="S27" s="58"/>
-      <c r="U27" t="s">
-        <v>180</v>
-      </c>
-      <c r="V27" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V27" s="65"/>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
@@ -3000,12 +2887,7 @@
       </c>
       <c r="R28" s="37"/>
       <c r="S28" s="58"/>
-      <c r="U28" t="s">
-        <v>181</v>
-      </c>
-      <c r="V28" s="65" t="s">
-        <v>153</v>
-      </c>
+      <c r="V28" s="65"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
@@ -3062,9 +2944,6 @@
       </c>
       <c r="R29" s="51"/>
       <c r="S29" s="58"/>
-      <c r="V29" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
@@ -3121,9 +3000,6 @@
       </c>
       <c r="R30" s="37"/>
       <c r="S30" s="58"/>
-      <c r="V30" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="31" spans="1:22" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
@@ -3180,9 +3056,6 @@
       </c>
       <c r="R31" s="51"/>
       <c r="S31" s="39"/>
-      <c r="V31" t="s">
-        <v>153</v>
-      </c>
     </row>
     <row r="32" spans="1:22" s="64" customFormat="1" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="63"/>
@@ -3239,9 +3112,7 @@
       </c>
       <c r="R32" s="51"/>
       <c r="S32" s="39"/>
-      <c r="V32" t="s">
-        <v>153</v>
-      </c>
+      <c r="V32"/>
     </row>
     <row r="33" spans="1:19" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
@@ -3327,20 +3198,9 @@
     <hyperlink ref="O12" r:id="rId21"/>
     <hyperlink ref="O25" r:id="rId22"/>
     <hyperlink ref="O32" r:id="rId23"/>
-    <hyperlink ref="V10" r:id="rId24"/>
-    <hyperlink ref="V11" r:id="rId25"/>
-    <hyperlink ref="V13" r:id="rId26"/>
-    <hyperlink ref="V14" r:id="rId27"/>
-    <hyperlink ref="V15" r:id="rId28"/>
-    <hyperlink ref="V16" r:id="rId29"/>
-    <hyperlink ref="V24" r:id="rId30"/>
-    <hyperlink ref="V23" r:id="rId31"/>
-    <hyperlink ref="V25" r:id="rId32"/>
-    <hyperlink ref="V27" r:id="rId33"/>
-    <hyperlink ref="V28" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId35"/>
-  <drawing r:id="rId36"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId24"/>
+  <drawing r:id="rId25"/>
 </worksheet>
 </file>